--- a/outputs/41348.xlsx
+++ b/outputs/41348.xlsx
@@ -226,20 +226,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,534 +439,534 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="18.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="14.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="18.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="0" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="0" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="0" t="n">
+      <c r="E2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>331709</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="4" t="n">
         <v>41580</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="4" t="n">
         <v>29040</v>
       </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H2,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H2,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="0" t="n">
+      <c r="E3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="n">
         <v>331709</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="N3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="3" t="n">
+      <c r="N3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="P3" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="Q3" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H3,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="Q3" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H3,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>5118.74</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>1615</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <v>331709</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="4" t="n">
         <v>41580</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="N4" s="4" t="n">
         <v>330</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O4" s="4" t="n">
         <v>29040</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H4,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="P4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H4,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="G5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="0" t="n">
+      <c r="G5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1" t="n">
         <v>331709</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="3" t="n">
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="P5" s="3" t="n">
+      <c r="P5" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="Q5" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H5,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="Q5" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H5,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>839</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>175612.07</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>129191</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <v>247673</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="4" t="n">
         <v>864999.5</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="4" t="n">
         <v>4153.07</v>
       </c>
-      <c r="O6" s="3" t="n">
+      <c r="O6" s="4" t="n">
         <v>219444.16075</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H6,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H6,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>411.5</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>81572.39</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>53307.5</v>
       </c>
-      <c r="H7" s="0" t="n">
+      <c r="H7" s="1" t="n">
         <v>247673</v>
       </c>
-      <c r="I7" s="0" t="s">
+      <c r="I7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="4" t="n">
         <v>864999.5</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="N7" s="4" t="n">
         <v>4153.07</v>
       </c>
-      <c r="O7" s="3" t="n">
+      <c r="O7" s="4" t="n">
         <v>219444.16075</v>
       </c>
-      <c r="P7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H7,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="P7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H7,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>10.4</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>1231.63</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>743.6</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="I8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H8,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H8,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="n">
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>4260.2</v>
       </c>
-      <c r="I9" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H9,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H9,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>127.7</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>141685.67</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>10430.2</v>
       </c>
-      <c r="I10" s="0" t="s">
+      <c r="I10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H10,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H10,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>250.9</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="n">
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>40947.3</v>
       </c>
-      <c r="I11" s="0" t="s">
+      <c r="I11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="1" t="str">
-        <f aca="false">IF(COUNTIFS($H:$H,$H11,$L:$L,"Technology",$I:$I,"Y")&gt;0,"Y","N")</f>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="2" t="str">
+        <f aca="false">IF(COUNTIFS($H$2:$H$11,H11,$L$2:$L$11,"Technology")&gt;0,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
